--- a/AAII_Financials/Quarterly/TU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>TU</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3464500</v>
+      </c>
+      <c r="E8" s="3">
         <v>3574100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3814400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3637800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3688800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3491100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3705100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3732200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3580200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3593500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3904200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3688800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3726000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3640000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3697500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3381400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3231600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3094200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3302700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3145200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2971700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3020000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3142200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3036700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2869000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2875600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2983000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3056700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2844600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2685900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2825900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2609500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2589600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2522600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2587600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2524400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2430600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2435300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2525900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2477500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2370600</v>
+        <v>2222400</v>
       </c>
       <c r="E9" s="3">
+        <v>2277400</v>
+      </c>
+      <c r="F9" s="3">
         <v>2498000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2331100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2399800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2239500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2463800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2413100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2322700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2273100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2539700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2357400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2455800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2404300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1490600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1265900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1197900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1137800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1411100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1197000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1140500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1139100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1320800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1222000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1101000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1070800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1293500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1231100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1156200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1080100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1357800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1224500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1122400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1059900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1216800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1132700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1059000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1017100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1209200</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1095500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1203600</v>
+        <v>1242200</v>
       </c>
       <c r="E10" s="3">
+        <v>1296700</v>
+      </c>
+      <c r="F10" s="3">
         <v>1316400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1306600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1289000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1251600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1241300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1319100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1257400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1320400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1364500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1331400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1270200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1235800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2206900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2115600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2033700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1956400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1891600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1948100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1831200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1880900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1821400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1814600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1768000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1804800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1689500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1825600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1688300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1605800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1468100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1385100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1467200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1462700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1370800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1391700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1371600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1418200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1316700</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1382000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>121100</v>
+        <v>1668200</v>
       </c>
       <c r="E14" s="3">
+        <v>214200</v>
+      </c>
+      <c r="F14" s="3">
         <v>4400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-73900</v>
       </c>
-      <c r="G14" s="3">
-        <v>462700</v>
-      </c>
       <c r="H14" s="3">
+        <v>428900</v>
+      </c>
+      <c r="I14" s="3">
         <v>45200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>28100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>62100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>164700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>55300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>223200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>82300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>42100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>69200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>56800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>21400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>28400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>32600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>46700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>27500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>30800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>54200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>44500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>54900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>47100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>30400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>24000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>21400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>25400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>35000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>21100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>17300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>21100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>10400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>700</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>8200</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>15400</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>28400</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>721800</v>
+      </c>
+      <c r="E15" s="3">
         <v>704900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>754100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>728700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>735400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>688100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>718600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>714300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>703600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>734800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>810200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>729600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>759700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>755400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>683800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>619400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>614100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>612100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>614500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>595600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>573500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>592400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>610500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>592600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>568900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>569200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>528600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>538100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>502000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>475000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>446000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>415700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>420800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>414000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>531400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>509000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>491900</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>508600</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>409500</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>395600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3072700</v>
+        <v>2942000</v>
       </c>
       <c r="E17" s="3">
+        <v>2979500</v>
+      </c>
+      <c r="F17" s="3">
         <v>3247700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3057000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3100800</v>
-      </c>
       <c r="H17" s="3">
+        <v>3133800</v>
+      </c>
+      <c r="I17" s="3">
         <v>2924800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3181000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3124500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3022000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3007100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3348400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3084800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3207200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3158100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3205000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2801400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2668500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2565600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2523900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2632600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2495800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2515400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2719000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2563600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2371500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2338700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2445000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2405900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2257700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2099300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2332000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2044900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2068700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1981300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2005600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1923000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1895200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2344600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2004300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>501500</v>
+        <v>522500</v>
       </c>
       <c r="E18" s="3">
+        <v>594600</v>
+      </c>
+      <c r="F18" s="3">
         <v>566700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>580800</v>
       </c>
-      <c r="G18" s="3">
-        <v>588000</v>
-      </c>
       <c r="H18" s="3">
+        <v>555000</v>
+      </c>
+      <c r="I18" s="3">
         <v>566300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>524000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>607700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>558200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>586400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>555800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>604000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>518800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>481900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>492500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>580100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>563100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>528500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>778900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>512600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>475900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>504600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>423200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>473000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>497500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>537000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>538000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>650800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>586800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>586600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>493900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>564600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>520900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>541300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>490400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>518700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>507600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>540100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>181300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>473200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-26500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-45900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8800</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-24300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>98400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>29200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>42100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-880600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>15500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>17000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-47100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>135500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>66500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-8400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-25700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-10300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-29100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>109400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>101200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>105700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>109100</v>
-      </c>
-      <c r="AO20" s="3">
-        <v>-3100</v>
       </c>
       <c r="AP20" s="3">
         <v>-3100</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>-3100</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1232900</v>
+        <v>1249200</v>
       </c>
       <c r="E21" s="3">
+        <v>1326100</v>
+      </c>
+      <c r="F21" s="3">
         <v>1322300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1355500</v>
       </c>
-      <c r="G21" s="3">
-        <v>1314700</v>
-      </c>
       <c r="H21" s="3">
+        <v>1281700</v>
+      </c>
+      <c r="I21" s="3">
         <v>1254400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1267000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1223600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1232600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1279100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2246700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1318100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1273200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1220200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1129200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1335100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1243700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1137000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1388900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1105900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1042200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1085000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1023700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1057200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1048400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1098300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1062700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1163200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1078500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1063900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>934600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>951200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>942500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>947800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1019600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1027000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1004700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1057900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>587700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>865800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>276700</v>
+      </c>
+      <c r="E22" s="3">
         <v>282300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>281500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>290000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>275000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>240700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>248800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>259800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>255700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>255500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1098700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>246900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>238600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>221700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>189900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>160300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>138200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>126500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>137700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>141500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>139600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>143400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>137000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>134900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>140500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>142900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>132500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>140900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>139600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>131600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>115700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>113400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>113700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>109900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>216600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>212100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>211400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>215100</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>99900</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>96000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1402700</v>
+      </c>
+      <c r="E23" s="3">
         <v>142600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>294600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>422100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-145200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>283900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>304400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>228700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>219200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>133700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>292300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>122000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>195600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>206200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>255400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>555300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>491400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>398400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>636700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>368900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>329100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>349100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>276200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>329700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>339000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>386200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>401500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>484200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>437000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>457300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>372900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>422200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>408000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>423800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>383300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>407800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>401900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>434000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>78400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>374100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-114100</v>
+      </c>
+      <c r="E24" s="3">
         <v>39400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>83100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>112700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>34500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>74400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>82000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>38500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>57700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>30300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>57500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>20700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>47600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>40700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>60400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>153800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>123400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>104700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>145900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>103700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>80300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>99100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>66500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>83600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>91800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>109100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>106000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>119400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>24600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>120900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>92900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>97400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>109200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>113700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>119800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>105700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>107200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>109900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>11500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1288600</v>
+      </c>
+      <c r="E26" s="3">
         <v>103200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>211500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>309400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-179600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>209400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>222400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>190200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>161500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>103400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>234700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>101300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>148000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>165600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>195100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>401500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>368000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>293700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>490900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>265200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>248800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>250000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>209700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>246100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>247200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>277100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>295500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>364800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>412400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>336400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>280100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>324800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>298900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>310100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>263500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>302100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>294700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>324200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>66800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>272700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1295700</v>
+      </c>
+      <c r="E27" s="3">
         <v>97400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>213000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>353900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>223300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>248800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>207300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>166600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>93800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>218100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>100500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>151000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>160400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>182600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>374600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>345800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>279900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>476800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>255600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>242300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>248500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>201200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>235400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>227600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>274800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>286900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>359000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>410000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>329500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>271700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>321900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>308600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>262700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>299900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>289500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>318000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>62200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>267300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E32" s="3">
         <v>26500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>45900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8800</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>24300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-98400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-29200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-42100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>880600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-15500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>47100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-135500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-66500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>12000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>10100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>8400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>18000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>25700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>10300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>29100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>7500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-109400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-101200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-105700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-109100</v>
-      </c>
-      <c r="AO32" s="3">
-        <v>3100</v>
       </c>
       <c r="AP32" s="3">
         <v>3100</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>3100</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1295700</v>
+      </c>
+      <c r="E33" s="3">
         <v>97400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>213000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>353900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>223300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>248800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>207300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>166600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>93800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>218100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>100500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>151000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>160400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>182600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>374600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>345800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>279900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>476800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>255600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>242300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>248500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>201200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>235400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>227600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>274800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>286900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>359000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>410000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>329500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>271700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>321900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>308600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>262700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>299900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>289500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>318000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>62200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>267300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1295700</v>
+      </c>
+      <c r="E35" s="3">
         <v>97400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>213000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>353900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>223300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>248800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>207300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>166600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>93800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>218100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>100500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>151000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>160400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>182600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>374600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>345800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>279900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>476800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>255600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>242300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>248500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>201200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>235400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>227600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>274800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>286900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>359000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>410000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>329500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>271700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>321900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>308600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>262700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>299900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>289500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>318000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>62200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>267300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,169 +4305,173 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>976700</v>
+      </c>
+      <c r="E41" s="3">
         <v>932800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1911600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1311700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2699700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>705500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>604000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>602500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>677300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1598100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>654200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>890000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>490100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>648200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>717000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1049400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>282300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>562700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>535300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1380700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1578800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1428900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>656100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>476100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>762000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>830600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>417100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>306700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>172100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>452700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>315100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>314700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>514200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>312400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>378800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>363200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>276100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>610000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>331900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>315000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>12900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2200</v>
-      </c>
-      <c r="H42" s="3">
-        <v>700</v>
       </c>
       <c r="I42" s="3">
         <v>700</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>2200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4463,862 +4553,886 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2942800</v>
+      </c>
+      <c r="E43" s="3">
         <v>3180100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3228700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2988800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3064800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2915800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2988500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2977200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2959100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2986400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3215900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2919200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2896800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2794500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2856800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2643900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2401700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2255200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2458000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2319300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2130600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2175200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2276400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2151200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2008900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2108600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2203300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2282400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2217300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1966900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1874600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1774600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1694500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1671900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1836000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1185500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1118500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1162300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1137000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1157700</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>324600</v>
+      </c>
+      <c r="E44" s="3">
         <v>328100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>351500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>326700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>355600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>393800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>437200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>364200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>387200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>398000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>366500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>406600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>438000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>431600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>395300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>363700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>322900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>373000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>331700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>245900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>262500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>316100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>314900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>268300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>262900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>288900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>340700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>304300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>264900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>276400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>286200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>245600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>248400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>261200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>282800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>264900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>238900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>251200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>244300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>201300</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>328900</v>
+      </c>
+      <c r="E45" s="3">
         <v>288700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>307000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>297200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>290400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>308200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>298900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>259800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>257200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>243700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>238500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>247600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>242400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>245400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>515300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>681400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>577900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>495800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>400500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>441500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>443300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>463300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>371400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>454600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>434700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>515000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>432700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>518200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>525800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>502700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>447500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>465100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>503600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>481800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>380300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>270900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>310300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>279600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>187400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>244300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5003200</v>
+      </c>
+      <c r="E46" s="3">
         <v>5134500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6106000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5304100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6836500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4678100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4609300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4533100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4687800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5611800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4780300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4836800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4476700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4487000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4484400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4738400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3584800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3686700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3725500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4387400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4415300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4383500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3618800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3350200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3468600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3743100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3393900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3411500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3180000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3198600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2923300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2799900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2960700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2727400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2877900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2084500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1943900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2303200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1900600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1918300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>880900</v>
+      </c>
+      <c r="E47" s="3">
         <v>874700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>848900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>805500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>790400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>730500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>735300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>757200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>684600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>655000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>625500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>567000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>536900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>440500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1188100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1053100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1019100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1076000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1120200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>889600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>802800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>801200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>811700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>672300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>603500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>591100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>600300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>430300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>462300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>455700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>458200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>367000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>359800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>351600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>360200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>72200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>70000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>70700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>63800</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>74500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12515300</v>
+      </c>
+      <c r="E48" s="3">
         <v>12577200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12731900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12655000</v>
       </c>
-      <c r="G48" s="3">
-        <v>12838600</v>
-      </c>
       <c r="H48" s="3">
+        <v>12837800</v>
+      </c>
+      <c r="I48" s="3">
         <v>12034600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12017300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12739200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12586100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12685000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13060400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12842000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13062200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12648100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12575700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12299300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12032200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11723000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11791000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11768100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11075400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11293700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11617100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11372300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11425000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11292200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11096300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11413500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10744600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>10254800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18404700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8673000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8816700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8643500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8460200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8323200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8113400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8171700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8038800</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>7910500</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20297900</v>
+      </c>
+      <c r="E49" s="3">
         <v>22231500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22454600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22210700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22702500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>21609200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>21654200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22835000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22555800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22040100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22549100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22078000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22569100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22242300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>20866500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>20590400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>18522000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>18082200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>18335800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>17303700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>16230500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>16877100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>17183400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15743000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15508000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>15504700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>14153300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>14395600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>13364800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>12234000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>23875400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11335600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11590000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11535000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>11084300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>11063400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>10964400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>10896600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>10871200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>10807500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>418300</v>
+      </c>
+      <c r="E52" s="3">
         <v>432000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>385100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>416400</v>
       </c>
-      <c r="G52" s="3">
-        <v>371700</v>
-      </c>
       <c r="H52" s="3">
+        <v>372500</v>
+      </c>
+      <c r="I52" s="3">
         <v>409800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>428100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>386400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>456700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>562000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>514900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>526300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>492400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>528500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>669100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>863600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>942200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>660900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>560500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>855600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>755000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>684000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>251500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>454600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>626200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1109300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>371900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>797500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>601100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>582000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>640800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>357500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>391500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>293600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>327500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>459900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>500100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>499300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>427900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>563100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40005600</v>
+      </c>
+      <c r="E54" s="3">
         <v>42163300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>43477600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42259600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>44453200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>40341600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40329700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42182200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>41874100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42542800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>42507000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41737200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>42045800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41231800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>39783800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>39544700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>36100400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35228700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35532800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35204400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33279000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34039500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33482500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>31592500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>31631300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>32240400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>29615800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>30448500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28352800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>26725100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>25159400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23533100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>24118600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23551000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>23110000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>22003300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>21591800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>21941400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>21302200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>21273800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>808400</v>
+      </c>
+      <c r="E57" s="3">
         <v>712100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>716200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>773900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>669400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>795200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>782600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>752100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>729200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>711900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>754200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>713400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>706800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>640800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1017300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>870100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>741200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>793200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>898100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>817000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>713800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>660000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>668500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>647000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>654500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>617800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>695500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>765200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>739900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>596600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>522100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>469400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>486300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>408800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>533600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>488900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>401900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>427100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>444000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>406400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3539900</v>
+      </c>
+      <c r="E58" s="3">
         <v>3591300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2940700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2960800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3996000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3549600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2898200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2627000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3199500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3707200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3116700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3313300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3278200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2294100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1947000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3145300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2531000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2189800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2251400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1766700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1455800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2017600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1185400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>897000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>519500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1039400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1116500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>959200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1319600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1417200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>712400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>653300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>844600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>716700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1119300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1084300</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1039700</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1141600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1096300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>729800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1456900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1573200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1501000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1431600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1450300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1385200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1415000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1331700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1375100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1345500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1329700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1278900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1285300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1221700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3131400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3187600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2910100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2788800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2975500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2925900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2544300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2510900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2715100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2725400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2632000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2502700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2533900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2533600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2390200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2141600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2452200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2256400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2140900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1917400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2097900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2225200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2159700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2081900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2263200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2220200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7519900</v>
+      </c>
+      <c r="E60" s="3">
         <v>7674100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7066500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7002000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7984000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7296800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6836100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6581300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7075600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7443900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7176900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7274800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7118300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5974800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6095700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7203100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6182400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5771700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6125000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5509600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4713900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5188400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4569000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4269400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3806000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4160000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4345900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4258000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4449600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4155500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3686700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3379100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3471900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3042800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3750800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3798400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3601200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3650600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3803500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>3356400</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18664200</v>
+      </c>
+      <c r="E61" s="3">
         <v>18703200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>20117100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18585100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>20475000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17442500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17857400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18879300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18169000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18091500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>17829400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>17358700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>17329700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>17791400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16559500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>15250800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13658000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13387900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13271000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13518500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>13031700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>12903500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14589800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13672300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14090800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14039800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13365100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13380900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11907200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11111600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10095900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9516700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9888600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9890200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>9121000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>9124800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>9114300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>9442300</v>
-      </c>
-      <c r="AO61" s="3">
-        <v>8914500</v>
       </c>
       <c r="AP61" s="3">
         <v>8914500</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>8914500</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>483800</v>
+      </c>
+      <c r="E62" s="3">
         <v>453500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>522200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>581500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>489800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>453600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>535200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>583300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>576500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>601100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>606500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>538900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>549800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>567600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4130300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4104400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3933600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4143200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4247400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4370400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4214900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4337700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5314100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4073200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4019400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3802000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3654300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3810300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3593200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3479600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3506300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3367500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3417700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3406400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3199400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2756600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2617400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2585900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2487500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2632000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>30084500</v>
+      </c>
+      <c r="E66" s="3">
         <v>30437900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31386000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>29680000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32647000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>28663200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>28655000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29652500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>29420200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29816400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29405700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28796200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28770600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28053000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27587200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>27316100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>24486400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23995700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>24341600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>24082900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22607100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23110000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24166500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22288500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22178300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22216900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21391800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21532900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>20023000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>18812900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17351300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>16321500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>16832400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>16393500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>16102500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>15708800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>15360500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>15701900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>15220200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>14912100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2046300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-290900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>71500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>359000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>461900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>855700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1056400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1326500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1541700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1804100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2146700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2332300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2634000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2816700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3021000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3286700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3317300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3162500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3151000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3190400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3127200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3239200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2872200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2999900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3072300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3663000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3407900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3915600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3671700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3421100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3405100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>3025200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3042800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2907300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2823500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2120300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2080800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2068100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1900600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2178700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9352200</v>
+      </c>
+      <c r="E76" s="3">
         <v>11147200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11505200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11395700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11159500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10858200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10856000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11674000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11550800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11821700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12200200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12062100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12390100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12274100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12196600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12228600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11614000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11233000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11191300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11121500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10671800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10929500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9316000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9303900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9453000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10023500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8224000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8915600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8329900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7912200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7808000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7211700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7286300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7157500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7007500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6294500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6231300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6239600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6082100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6361700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1295700</v>
+      </c>
+      <c r="E81" s="3">
         <v>97400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>213000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>353900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>223300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>248800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>207300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>166600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>93800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>218100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>100500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>151000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>160400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>182600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>374600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>345800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>279900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>476800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>255600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>242300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>248500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>201200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>235400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>227600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>274800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>286900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>359000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>410000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>329500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>271700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>321900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>308600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>262700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>299900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>289500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>318000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>62200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>267300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>439900</v>
+      </c>
+      <c r="E83" s="3">
         <v>409800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>50000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>439700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>444200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>459300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-20400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>451700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>451600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>434600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>87900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>400600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>416100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>673600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>683800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>619400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>614100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>612100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>614500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>595600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>573500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>592400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>610500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>592600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>568900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>569200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>528600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>538100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>502000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>475000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>446000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>415700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>420800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>414000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>419700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>407100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>391500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>408700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>409500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>395600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>945000</v>
+      </c>
+      <c r="E89" s="3">
         <v>752200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>824100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1071900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>854900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>749300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>748500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1060000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1014100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>701600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>995000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>966200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>843500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>562400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>828900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>947400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>923700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>825200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>649300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>979300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>904000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>705100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>799300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>691500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1147300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>924000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>646300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>951700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>919900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>608200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>721500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>774700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>907900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>630800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>728600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>843200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>838000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>544700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>562300</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>792800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-420400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-542300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-276400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-530600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-438500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-455000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-558100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-459700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-486600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-599700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-839000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-519700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-626000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-721400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1049000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1225000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1131000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-907000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2638000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1650000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-544600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-437000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-479700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-580300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-543800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-472600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-556700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-581200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-569400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-491900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-448300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-460700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-481000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-392200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-433100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-503800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-487500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1115500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-581600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-607700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-473200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-819600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-499600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-473800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-801400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-418800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-466300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-578900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-917000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-732600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-542200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-584700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-685700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1724300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-628600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1397000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1062700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-871700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1472600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1084400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-622000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-865700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1707700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-901600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-645800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1537900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1256000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-722100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1268800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-740600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-478700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-451300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-598500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-701600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-546300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-644500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-908700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-631500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-651500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-522400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>305600</v>
+      </c>
+      <c r="E96" s="3">
         <v>308100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>301200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>292900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>297000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>279700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>269700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>284200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>314900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>265100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>256700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>249900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>241700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>235000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-226700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-216400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-214300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-213000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-201400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-200700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-181500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-188500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-182600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-177900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-188300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-174300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-173900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-262000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-243500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-233300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-221500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-212900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-209300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-210000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-200200</v>
       </c>
       <c r="AL96" s="3">
         <v>-200200</v>
       </c>
       <c r="AM96" s="3">
+        <v>-200200</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-193500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-218200</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-209000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-210500</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-411900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-877600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>254500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1929800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1902700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-229600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-243900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-564800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1001000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>991000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-710300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>28800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-330000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1090200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-543200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1220700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-150800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>83600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-35500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-117000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-79600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>952800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1084000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-58300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-569700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1024500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>738300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-102800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>54700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>266400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-257200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-505000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-107600</v>
       </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
       <c r="AK100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-166700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-111600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-244100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>364900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>106000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-284200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-944900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>579100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1331800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1956200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>100900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>38200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-83600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-903800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>960000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-257500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>410300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-172200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-71700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-343000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>771000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-289700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>37100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-844800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-236300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>202500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>792200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>175600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-268300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-68300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>410600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>128600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>126800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-294200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>133900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-14500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-181700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>201700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-70800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>15600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>87100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-314800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>278100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>16900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-13800</v>
       </c>
     </row>
